--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.beta.natif/Resultats_ratio.beta.natif_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.beta.natif/Resultats_ratio.beta.natif_moy_ADJR2.xlsx
@@ -1,208 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.beta.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV0_ADJR2</t>
-  </si>
-  <si>
-    <t>LV1_ADJR2</t>
-  </si>
-  <si>
-    <t>LV2_ADJR2</t>
-  </si>
-  <si>
-    <t>LV3_ADJR2</t>
-  </si>
-  <si>
-    <t>LV4_ADJR2</t>
-  </si>
-  <si>
-    <t>LV5_ADJR2</t>
-  </si>
-  <si>
-    <t>LV6_ADJR2</t>
-  </si>
-  <si>
-    <t>LV7_ADJR2</t>
-  </si>
-  <si>
-    <t>LV8_ADJR2</t>
-  </si>
-  <si>
-    <t>LV9_ADJR2</t>
-  </si>
-  <si>
-    <t>LV10_ADJR2</t>
-  </si>
-  <si>
-    <t>LV11_ADJR2</t>
-  </si>
-  <si>
-    <t>LV12_ADJR2</t>
-  </si>
-  <si>
-    <t>LV13_ADJR2</t>
-  </si>
-  <si>
-    <t>LV14_ADJR2</t>
-  </si>
-  <si>
-    <t>LV15_ADJR2</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -235,81 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -351,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -383,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -418,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -594,2310 +350,2408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_ADJR2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_ADJR2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_ADJR2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_ADJR2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_ADJR2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_ADJR2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_ADJR2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_ADJR2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_ADJR2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_ADJR2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_ADJR2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_ADJR2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_ADJR2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_ADJR2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_ADJR2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_ADJR2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C2">
-        <v>-5.2550455621270413E-2</v>
+        <v>-0.0525504570589698</v>
       </c>
       <c r="D2">
-        <v>-9.7262612983411975E-2</v>
+        <v>-0.09726264733231905</v>
       </c>
       <c r="E2">
-        <v>-8.8943127082720327E-2</v>
+        <v>-0.08894315736859984</v>
       </c>
       <c r="F2">
-        <v>-6.9106367497370189E-2</v>
+        <v>-0.06910635072408304</v>
       </c>
       <c r="G2">
-        <v>-9.2374790880846325E-2</v>
+        <v>-0.09237489742648178</v>
       </c>
       <c r="H2">
-        <v>-9.0760157505488548E-2</v>
+        <v>-0.09076019643995226</v>
       </c>
       <c r="I2">
-        <v>-3.121954025894625E-2</v>
+        <v>-0.0312195403326116</v>
       </c>
       <c r="J2">
-        <v>2.457360742735135E-2</v>
+        <v>0.02457360975732188</v>
       </c>
       <c r="K2">
-        <v>-2.88328434776596E-3</v>
+        <v>-0.00288327660952358</v>
       </c>
       <c r="L2">
-        <v>4.0909238273259103E-2</v>
+        <v>0.04090923250925116</v>
       </c>
       <c r="M2">
-        <v>0.1228394107623119</v>
+        <v>0.1228394212798865</v>
       </c>
       <c r="N2">
-        <v>0.14771589886262829</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0.25209421445845759</v>
+        <v>0.1477158906075284</v>
+      </c>
+      <c r="O2">
+        <v>0.2520942031007456</v>
       </c>
       <c r="P2">
-        <v>0.34383847846306032</v>
+        <v>0.3438384949013176</v>
       </c>
       <c r="Q2">
-        <v>0.38130390027101418</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
+        <v>0.3813039034077526</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C3">
-        <v>-2.520547656425379E-2</v>
+        <v>-0.02520548533565767</v>
       </c>
       <c r="D3">
-        <v>-0.20794065501162759</v>
+        <v>-0.2079407317742066</v>
       </c>
       <c r="E3">
-        <v>-0.14325961226426781</v>
+        <v>-0.1432596410216352</v>
       </c>
       <c r="F3">
-        <v>9.086766115276132E-3</v>
+        <v>0.009086673247461239</v>
       </c>
       <c r="G3">
-        <v>9.9040304141408228E-2</v>
+        <v>0.09904028410160147</v>
       </c>
       <c r="H3">
-        <v>0.1476116495900314</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.20435468726528189</v>
+        <v>0.1476115157144407</v>
+      </c>
+      <c r="I3">
+        <v>0.2043544882144198</v>
       </c>
       <c r="J3">
-        <v>0.23349003287455419</v>
+        <v>0.2334900921548881</v>
       </c>
       <c r="K3">
-        <v>0.28105071595194159</v>
+        <v>0.2810507647192237</v>
       </c>
       <c r="L3">
-        <v>0.30996570516911381</v>
+        <v>0.309965777061986</v>
       </c>
       <c r="M3">
-        <v>0.30192263969268091</v>
+        <v>0.3019227367327608</v>
       </c>
       <c r="N3">
-        <v>0.29543928794617891</v>
+        <v>0.2954394407041798</v>
       </c>
       <c r="O3">
-        <v>0.2736782547501706</v>
+        <v>0.2736785254289656</v>
       </c>
       <c r="P3">
-        <v>0.25842696411123139</v>
+        <v>0.2584271730602155</v>
       </c>
       <c r="Q3">
-        <v>0.27991452256752147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
+        <v>0.2799153744899939</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C4">
-        <v>-4.5362881162091188E-2</v>
+        <v>-0.04536288560608748</v>
       </c>
       <c r="D4">
-        <v>-6.770439059669639E-2</v>
+        <v>-0.0677044085089616</v>
       </c>
       <c r="E4">
-        <v>-0.14118532739277351</v>
+        <v>-0.1411853496648705</v>
       </c>
       <c r="F4">
-        <v>-0.14990509074341299</v>
+        <v>-0.1499051244692251</v>
       </c>
       <c r="G4">
-        <v>-0.21003954240716219</v>
+        <v>-0.2100395231247637</v>
       </c>
       <c r="H4">
-        <v>-8.1316683024048222E-2</v>
+        <v>-0.08131665222437376</v>
       </c>
       <c r="I4">
-        <v>3.8107845748587549E-4</v>
+        <v>0.0003810720165899535</v>
       </c>
       <c r="J4">
-        <v>4.5464768026364809E-2</v>
+        <v>0.04546476684726843</v>
       </c>
       <c r="K4">
-        <v>5.6033882293843373E-2</v>
+        <v>0.05603393862079386</v>
       </c>
       <c r="L4">
-        <v>0.12524095833079679</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0.20040786683933079</v>
+        <v>0.1252409571321875</v>
+      </c>
+      <c r="M4">
+        <v>0.2004078909851574</v>
       </c>
       <c r="N4">
-        <v>0.25918862700745299</v>
+        <v>0.2591886520723851</v>
       </c>
       <c r="O4">
-        <v>0.29492491710344348</v>
+        <v>0.2949249354369885</v>
       </c>
       <c r="P4">
-        <v>0.29557952089133449</v>
+        <v>0.295579535519684</v>
       </c>
       <c r="Q4">
-        <v>0.27928754637975339</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
+        <v>0.2792875614149997</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C5">
-        <v>-3.6196279957058972E-2</v>
+        <v>-0.03619628968195818</v>
       </c>
       <c r="D5">
-        <v>-0.1034457650343157</v>
+        <v>-0.1034458043020717</v>
       </c>
       <c r="E5">
-        <v>-5.3856692236063528E-2</v>
+        <v>-0.05385667632810764</v>
       </c>
       <c r="F5">
-        <v>-0.146869735741334</v>
+        <v>-0.1468697177841119</v>
       </c>
       <c r="G5">
-        <v>4.6525633420117493E-2</v>
+        <v>0.04652562075437745</v>
       </c>
       <c r="H5">
-        <v>0.1355329518759654</v>
+        <v>0.1355329551981707</v>
       </c>
       <c r="I5">
-        <v>0.18098017188891349</v>
+        <v>0.180980186462174</v>
       </c>
       <c r="J5">
-        <v>0.25303828014880841</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0.32566059395220498</v>
+        <v>0.2530382670678211</v>
+      </c>
+      <c r="K5">
+        <v>0.3256606313607198</v>
       </c>
       <c r="L5">
-        <v>0.35412591642843461</v>
+        <v>0.3541259928862528</v>
       </c>
       <c r="M5">
-        <v>0.38514256997671148</v>
+        <v>0.3851426476103639</v>
       </c>
       <c r="N5">
-        <v>0.38662542466574967</v>
+        <v>0.3866255202162721</v>
       </c>
       <c r="O5">
-        <v>0.36037627327054722</v>
+        <v>0.3603763917537315</v>
       </c>
       <c r="P5">
-        <v>0.34411208266266641</v>
+        <v>0.3441122378749197</v>
       </c>
       <c r="Q5">
-        <v>0.31896084964283228</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
+        <v>0.3189610398325159</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C6">
-        <v>-3.8196498543364168E-2</v>
+        <v>-0.03819650300577714</v>
       </c>
       <c r="D6">
-        <v>-0.1283806882142659</v>
+        <v>-0.1283807460847644</v>
       </c>
       <c r="E6">
-        <v>-8.111162612341738E-2</v>
+        <v>-0.08111164889141156</v>
       </c>
       <c r="F6">
-        <v>-0.1133309657243551</v>
+        <v>-0.1133309393317038</v>
       </c>
       <c r="G6">
-        <v>0.1072755543189112</v>
+        <v>0.107276185080831</v>
       </c>
       <c r="H6">
-        <v>0.2099322515226103</v>
+        <v>0.2099271047514243</v>
       </c>
       <c r="I6">
-        <v>0.26266255994205479</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0.34480566961040682</v>
+        <v>0.2626623346512886</v>
+      </c>
+      <c r="J6">
+        <v>0.3448056798671563</v>
       </c>
       <c r="K6">
-        <v>0.3836101171600404</v>
+        <v>0.3836099429026816</v>
       </c>
       <c r="L6">
-        <v>0.39448610989078031</v>
+        <v>0.3944860196947808</v>
       </c>
       <c r="M6">
-        <v>0.41465166640704532</v>
+        <v>0.4146516791894123</v>
       </c>
       <c r="N6">
-        <v>0.42169368994676909</v>
+        <v>0.4216937088718359</v>
       </c>
       <c r="O6">
-        <v>0.41111007261017052</v>
+        <v>0.4111101011280408</v>
       </c>
       <c r="P6">
-        <v>0.41788249925015619</v>
+        <v>0.4178825470984849</v>
       </c>
       <c r="Q6">
-        <v>0.39590815387857031</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
+        <v>0.3959081702181699</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C7">
-        <v>-4.623755128213497E-2</v>
+        <v>-0.04623755077331253</v>
       </c>
       <c r="D7">
-        <v>-6.9633730633971963E-2</v>
+        <v>-0.06963376516336067</v>
       </c>
       <c r="E7">
-        <v>-0.13723371920790839</v>
+        <v>-0.1372337020581546</v>
       </c>
       <c r="F7">
-        <v>-0.16144648933783401</v>
+        <v>-0.1614464559060892</v>
       </c>
       <c r="G7">
-        <v>-0.23232668064604359</v>
+        <v>-0.2323266921095054</v>
       </c>
       <c r="H7">
-        <v>-0.17633914031345341</v>
+        <v>-0.1763390861388491</v>
       </c>
       <c r="I7">
-        <v>-6.5106042751975027E-2</v>
+        <v>-0.06510603389234361</v>
       </c>
       <c r="J7">
-        <v>3.2541317110493038E-2</v>
+        <v>0.03254140081936227</v>
       </c>
       <c r="K7">
-        <v>5.9119869551080943E-2</v>
+        <v>0.05911993086465982</v>
       </c>
       <c r="L7">
-        <v>7.2107725656528135E-2</v>
+        <v>0.07210780759552989</v>
       </c>
       <c r="M7">
-        <v>0.17740569904209849</v>
-      </c>
-      <c r="N7" s="2">
-        <v>0.24849207217568531</v>
+        <v>0.1774057437389592</v>
+      </c>
+      <c r="N7">
+        <v>0.2484920888897174</v>
       </c>
       <c r="O7">
-        <v>0.3060363177200251</v>
+        <v>0.3060356609494145</v>
       </c>
       <c r="P7">
-        <v>0.32929436217281483</v>
+        <v>0.3292943642673338</v>
       </c>
       <c r="Q7">
-        <v>0.33328488692686392</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
+        <v>0.3332848949405223</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C8">
-        <v>-4.2673853363968423E-2</v>
+        <v>-0.0426738555420671</v>
       </c>
       <c r="D8">
-        <v>-7.3376073367082864E-2</v>
+        <v>-0.07337608607792945</v>
       </c>
       <c r="E8">
-        <v>-0.1459922276099366</v>
+        <v>-0.1459922759441168</v>
       </c>
       <c r="F8">
-        <v>-0.19586100180913379</v>
+        <v>-0.1958609614500488</v>
       </c>
       <c r="G8">
-        <v>-0.126923973801981</v>
+        <v>-0.1269239591925504</v>
       </c>
       <c r="H8">
-        <v>-1.904248483229137E-2</v>
+        <v>-0.01904248318954493</v>
       </c>
       <c r="I8">
-        <v>-2.2355301947548801E-3</v>
+        <v>-0.002235562014085496</v>
       </c>
       <c r="J8">
-        <v>0.1029725941298978</v>
+        <v>0.1029726424305178</v>
       </c>
       <c r="K8">
-        <v>0.14863820911505479</v>
-      </c>
-      <c r="L8" s="2">
-        <v>0.26460285858376043</v>
+        <v>0.1486382434698122</v>
+      </c>
+      <c r="L8">
+        <v>0.2646028780032628</v>
       </c>
       <c r="M8">
-        <v>0.28160962104249609</v>
+        <v>0.2816096261027101</v>
       </c>
       <c r="N8">
-        <v>0.32346500604366318</v>
+        <v>0.3234650917294846</v>
       </c>
       <c r="O8">
-        <v>0.34783089545000517</v>
+        <v>0.3478309591799574</v>
       </c>
       <c r="P8">
-        <v>0.3475324971200453</v>
+        <v>0.3475324965388339</v>
       </c>
       <c r="Q8">
-        <v>0.33539573160720548</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
+        <v>0.3353957400654564</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C9">
-        <v>-3.9285169840428992E-2</v>
+        <v>-0.0392851718109027</v>
       </c>
       <c r="D9">
-        <v>-6.3087191800144285E-2</v>
+        <v>-0.06308720863013943</v>
       </c>
       <c r="E9">
-        <v>-0.13102076231499249</v>
+        <v>-0.1310208166208371</v>
       </c>
       <c r="F9">
-        <v>-0.16219552552984851</v>
+        <v>-0.1621954838496257</v>
       </c>
       <c r="G9">
-        <v>-0.1121480774895057</v>
+        <v>-0.1121480819464938</v>
       </c>
       <c r="H9">
-        <v>-7.6805907088194946E-3</v>
+        <v>-0.007680570117908383</v>
       </c>
       <c r="I9">
-        <v>4.2001986300394421E-3</v>
+        <v>0.004200271088157556</v>
       </c>
       <c r="J9">
-        <v>0.10493091618121191</v>
+        <v>0.1049309746325457</v>
       </c>
       <c r="K9">
-        <v>0.13483337434169429</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0.28961142760915748</v>
+        <v>0.134833267097438</v>
+      </c>
+      <c r="L9">
+        <v>0.2896114288928368</v>
       </c>
       <c r="M9">
-        <v>0.28161941890949738</v>
+        <v>0.2816194239827732</v>
       </c>
       <c r="N9">
-        <v>0.32754532377898388</v>
+        <v>0.3275453299768065</v>
       </c>
       <c r="O9">
-        <v>0.35574802544189782</v>
+        <v>0.355748020646282</v>
       </c>
       <c r="P9">
-        <v>0.35180341579378138</v>
+        <v>0.3518034133801462</v>
       </c>
       <c r="Q9">
-        <v>0.34988188635983603</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
+        <v>0.3498818614651322</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C10">
-        <v>-4.1779834522308303E-2</v>
+        <v>-0.0417798359641264</v>
       </c>
       <c r="D10">
-        <v>-7.3127840685657808E-2</v>
+        <v>-0.07312789593984298</v>
       </c>
       <c r="E10">
-        <v>-0.13886532314941949</v>
+        <v>-0.138865327780582</v>
       </c>
       <c r="F10">
-        <v>-0.16490607969977239</v>
+        <v>-0.1649060286499661</v>
       </c>
       <c r="G10">
-        <v>-0.1133516710871387</v>
+        <v>-0.1133516526481938</v>
       </c>
       <c r="H10">
-        <v>-6.0015388342727748E-3</v>
+        <v>-0.006001523695810962</v>
       </c>
       <c r="I10">
-        <v>7.2144518880046882E-3</v>
+        <v>0.007214511985555791</v>
       </c>
       <c r="J10">
-        <v>0.1066167670939992</v>
+        <v>0.1066168296348121</v>
       </c>
       <c r="K10">
-        <v>0.14187817889841511</v>
-      </c>
-      <c r="L10" s="2">
-        <v>0.29097238532242858</v>
+        <v>0.1418782435589497</v>
+      </c>
+      <c r="L10">
+        <v>0.2909723895970474</v>
       </c>
       <c r="M10">
-        <v>0.27886399032473869</v>
+        <v>0.2788639085947742</v>
       </c>
       <c r="N10">
-        <v>0.32266084205467799</v>
+        <v>0.3226608032018756</v>
       </c>
       <c r="O10">
-        <v>0.34904949561936821</v>
+        <v>0.3490494895115884</v>
       </c>
       <c r="P10">
-        <v>0.34034208471476141</v>
+        <v>0.3403420732222351</v>
       </c>
       <c r="Q10">
-        <v>0.33578147406989273</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
+        <v>0.3357813903376272</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C11">
-        <v>-3.8685697977049002E-2</v>
+        <v>-0.03868570147619046</v>
       </c>
       <c r="D11">
-        <v>-6.8394876199665278E-2</v>
+        <v>-0.0683949279865558</v>
       </c>
       <c r="E11">
-        <v>-0.13439265531976141</v>
+        <v>-0.1343926533912133</v>
       </c>
       <c r="F11">
-        <v>-0.16539713944553661</v>
+        <v>-0.1653982286726546</v>
       </c>
       <c r="G11">
-        <v>-0.11469064085100091</v>
+        <v>-0.1146908010845094</v>
       </c>
       <c r="H11">
-        <v>-1.0331245414816869E-2</v>
+        <v>-0.01033122647374164</v>
       </c>
       <c r="I11">
-        <v>-3.708819364246144E-3</v>
+        <v>-0.003708821559060391</v>
       </c>
       <c r="J11">
-        <v>9.5693243121426144E-2</v>
+        <v>0.09569327507603871</v>
       </c>
       <c r="K11">
-        <v>0.1218998373463319</v>
-      </c>
-      <c r="L11" s="2">
-        <v>0.27736340438627771</v>
+        <v>0.1218998281746765</v>
+      </c>
+      <c r="L11">
+        <v>0.2773634209817811</v>
       </c>
       <c r="M11">
-        <v>0.28067446199123858</v>
+        <v>0.2806744691825745</v>
       </c>
       <c r="N11">
-        <v>0.32740179356263022</v>
+        <v>0.3274018017917169</v>
       </c>
       <c r="O11">
-        <v>0.35578450654795929</v>
+        <v>0.3557845085482018</v>
       </c>
       <c r="P11">
-        <v>0.34849370378270222</v>
+        <v>0.3484936984948782</v>
       </c>
       <c r="Q11">
-        <v>0.34759086815231671</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
+        <v>0.3475908565513051</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C12">
-        <v>-3.07377212545616E-2</v>
+        <v>-0.03073772668483738</v>
       </c>
       <c r="D12">
-        <v>-9.8122392847992582E-2</v>
+        <v>-0.09812243111233199</v>
       </c>
       <c r="E12">
-        <v>-6.0318999109531903E-2</v>
+        <v>-0.06031899156216847</v>
       </c>
       <c r="F12">
-        <v>-0.15043543431820011</v>
+        <v>-0.1504354025806371</v>
       </c>
       <c r="G12">
-        <v>4.029505779682914E-2</v>
+        <v>0.04029502459118318</v>
       </c>
       <c r="H12">
-        <v>9.4786450481839785E-2</v>
+        <v>0.09478641066066187</v>
       </c>
       <c r="I12">
-        <v>0.21260154222858349</v>
+        <v>0.2126015647653736</v>
       </c>
       <c r="J12">
-        <v>0.31127945018260228</v>
-      </c>
-      <c r="K12" s="2">
-        <v>0.37009438443267861</v>
+        <v>0.3112794625064413</v>
+      </c>
+      <c r="K12">
+        <v>0.3700944416458671</v>
       </c>
       <c r="L12">
-        <v>0.39678182717370369</v>
+        <v>0.3967818867625385</v>
       </c>
       <c r="M12">
-        <v>0.42460790941895121</v>
+        <v>0.4246079905018054</v>
       </c>
       <c r="N12">
-        <v>0.42744942495337668</v>
+        <v>0.4274495212981363</v>
       </c>
       <c r="O12">
-        <v>0.40381215071444931</v>
+        <v>0.4038122634941254</v>
       </c>
       <c r="P12">
-        <v>0.37888161671188447</v>
+        <v>0.3788817468959714</v>
       </c>
       <c r="Q12">
-        <v>0.3322910541705979</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
+        <v>0.3322912320495728</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C13">
-        <v>-4.474374794869912E-2</v>
+        <v>-0.04474377255383943</v>
       </c>
       <c r="D13">
-        <v>-0.18722925589868869</v>
+        <v>-0.1872292765930972</v>
       </c>
       <c r="E13">
-        <v>-0.1190689446765482</v>
+        <v>-0.119068908798744</v>
       </c>
       <c r="F13">
-        <v>-0.17176007684116509</v>
+        <v>-0.1717601336700974</v>
       </c>
       <c r="G13">
-        <v>-0.16188475811797801</v>
+        <v>-0.1618847706139838</v>
       </c>
       <c r="H13">
-        <v>-1.039567584252598E-2</v>
+        <v>-0.01039599816157557</v>
       </c>
       <c r="I13">
-        <v>-8.0430393550000694E-3</v>
+        <v>-0.008035211101404111</v>
       </c>
       <c r="J13">
-        <v>4.2226140852033793E-2</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0.12680739422929521</v>
+        <v>0.04224432285971164</v>
+      </c>
+      <c r="K13">
+        <v>0.1268066109086421</v>
       </c>
       <c r="L13">
-        <v>0.20353410465515209</v>
+        <v>0.2035341788033152</v>
       </c>
       <c r="M13">
-        <v>0.21531714394567469</v>
+        <v>0.2153171929595021</v>
       </c>
       <c r="N13">
-        <v>0.24917624610613559</v>
+        <v>0.2491762895130971</v>
       </c>
       <c r="O13">
-        <v>0.24961161216950301</v>
+        <v>0.2496116913798981</v>
       </c>
       <c r="P13">
-        <v>0.26830841625161772</v>
+        <v>0.268308537975345</v>
       </c>
       <c r="Q13">
-        <v>0.2553426943076092</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
+        <v>0.2553428776850714</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C14">
-        <v>-4.8530708546551497E-2</v>
+        <v>-0.0485307113222338</v>
       </c>
       <c r="D14">
-        <v>-7.0860743443451946E-2</v>
+        <v>-0.07086074690430279</v>
       </c>
       <c r="E14">
-        <v>-0.1362511767694711</v>
+        <v>-0.1362510718841817</v>
       </c>
       <c r="F14">
-        <v>-0.14926044016438519</v>
+        <v>-0.1492605492032232</v>
       </c>
       <c r="G14">
-        <v>-0.2110316110340095</v>
+        <v>-0.2110318020721557</v>
       </c>
       <c r="H14">
-        <v>-0.17213963729386059</v>
+        <v>-0.1721395642963136</v>
       </c>
       <c r="I14">
-        <v>-6.0199183800457488E-2</v>
+        <v>-0.0601991833924387</v>
       </c>
       <c r="J14">
-        <v>3.4693740368685409E-2</v>
+        <v>0.03469376790751202</v>
       </c>
       <c r="K14">
-        <v>6.5479670574415991E-2</v>
+        <v>0.0654796851295818</v>
       </c>
       <c r="L14">
-        <v>7.7274837896374834E-2</v>
+        <v>0.07727488304994044</v>
       </c>
       <c r="M14">
-        <v>0.18684634558143309</v>
-      </c>
-      <c r="N14" s="2">
-        <v>0.29917290069171609</v>
+        <v>0.1868463180974572</v>
+      </c>
+      <c r="N14">
+        <v>0.2991729286296453</v>
       </c>
       <c r="O14">
-        <v>0.34173342144896152</v>
+        <v>0.3417335175767596</v>
       </c>
       <c r="P14">
-        <v>0.36844467332926051</v>
+        <v>0.3684446654400128</v>
       </c>
       <c r="Q14">
-        <v>0.38396338506653421</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>30</v>
+        <v>0.3839633742504509</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C15">
-        <v>-4.9973465672468402E-2</v>
+        <v>-0.0499734667467417</v>
       </c>
       <c r="D15">
-        <v>-7.0829884027051912E-2</v>
+        <v>-0.07082991938337235</v>
       </c>
       <c r="E15">
-        <v>-0.13746554426917021</v>
+        <v>-0.137465566681123</v>
       </c>
       <c r="F15">
-        <v>-0.15591149191897949</v>
+        <v>-0.1559114821328548</v>
       </c>
       <c r="G15">
-        <v>-0.2188626146343019</v>
+        <v>-0.2188625854258263</v>
       </c>
       <c r="H15">
-        <v>-0.16950353681773839</v>
+        <v>-0.1695034957158657</v>
       </c>
       <c r="I15">
-        <v>-6.2961323368463162E-2</v>
+        <v>-0.06296130691845978</v>
       </c>
       <c r="J15">
-        <v>2.467543644693317E-2</v>
+        <v>0.02467540993499724</v>
       </c>
       <c r="K15">
-        <v>4.5835795891743053E-2</v>
+        <v>0.04583580138333342</v>
       </c>
       <c r="L15">
-        <v>6.3907474188459185E-2</v>
+        <v>0.06390744093550783</v>
       </c>
       <c r="M15">
-        <v>0.16147322343166551</v>
-      </c>
-      <c r="N15" s="2">
-        <v>0.25752096561330567</v>
+        <v>0.1614732819345103</v>
+      </c>
+      <c r="N15">
+        <v>0.2575209720402116</v>
       </c>
       <c r="O15">
-        <v>0.29927885338507881</v>
+        <v>0.2992788557266588</v>
       </c>
       <c r="P15">
-        <v>0.32602999475238598</v>
+        <v>0.3260299941683436</v>
       </c>
       <c r="Q15">
-        <v>0.34406009728547932</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
+        <v>0.3440600943364074</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C16">
-        <v>-4.3423031325673732E-2</v>
+        <v>-0.04342303381838538</v>
       </c>
       <c r="D16">
-        <v>-6.6219779817027133E-2</v>
+        <v>-0.06621980451526324</v>
       </c>
       <c r="E16">
-        <v>-0.1367475910954758</v>
+        <v>-0.1367475988554234</v>
       </c>
       <c r="F16">
-        <v>-0.15716085490876239</v>
+        <v>-0.1571608980795866</v>
       </c>
       <c r="G16">
-        <v>-0.21760505993503071</v>
+        <v>-0.2176051843777129</v>
       </c>
       <c r="H16">
-        <v>-0.18063204050410761</v>
+        <v>-0.1806323935789385</v>
       </c>
       <c r="I16">
-        <v>-7.1782090712815189E-2</v>
+        <v>-0.07178205981645921</v>
       </c>
       <c r="J16">
-        <v>1.2644273002369991E-2</v>
+        <v>0.0126443063048137</v>
       </c>
       <c r="K16">
-        <v>3.9889185259313703E-2</v>
+        <v>0.03988917710664959</v>
       </c>
       <c r="L16">
-        <v>5.3307695413271503E-2</v>
+        <v>0.05330762618184193</v>
       </c>
       <c r="M16">
-        <v>0.14590876932473901</v>
-      </c>
-      <c r="N16" s="2">
-        <v>0.26259066350339078</v>
+        <v>0.1459087624965847</v>
+      </c>
+      <c r="N16">
+        <v>0.2625906384514897</v>
       </c>
       <c r="O16">
-        <v>0.29983502239991039</v>
+        <v>0.2998350247043411</v>
       </c>
       <c r="P16">
-        <v>0.32945520068508882</v>
+        <v>0.3294551960765187</v>
       </c>
       <c r="Q16">
-        <v>0.35548841210065107</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
+        <v>0.3554883964414501</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C17">
-        <v>-4.7482754665521328E-2</v>
+        <v>-0.04748275550597331</v>
       </c>
       <c r="D17">
-        <v>-7.1536980033520312E-2</v>
+        <v>-0.07153699480586166</v>
       </c>
       <c r="E17">
-        <v>-0.1374591323891203</v>
+        <v>-0.137459134957189</v>
       </c>
       <c r="F17">
-        <v>-0.15430375068594679</v>
+        <v>-0.1543038022816567</v>
       </c>
       <c r="G17">
-        <v>-0.2166419079545511</v>
+        <v>-0.2166419210660739</v>
       </c>
       <c r="H17">
-        <v>-0.1745681454940976</v>
+        <v>-0.1745683776021254</v>
       </c>
       <c r="I17">
-        <v>-6.8376193726815429E-2</v>
+        <v>-0.06837618740300459</v>
       </c>
       <c r="J17">
-        <v>1.221897339123898E-2</v>
+        <v>0.01221879541191096</v>
       </c>
       <c r="K17">
-        <v>3.2465016259714423E-2</v>
+        <v>0.03246501875467147</v>
       </c>
       <c r="L17">
-        <v>4.7377061847419681E-2</v>
+        <v>0.04737708027388935</v>
       </c>
       <c r="M17">
-        <v>0.14108651132804129</v>
-      </c>
-      <c r="N17" s="2">
-        <v>0.2382178486985527</v>
+        <v>0.1410863021059587</v>
+      </c>
+      <c r="N17">
+        <v>0.2382178343433048</v>
       </c>
       <c r="O17">
-        <v>0.2727439719867894</v>
+        <v>0.2727439768006595</v>
       </c>
       <c r="P17">
-        <v>0.30087462320269981</v>
+        <v>0.3008746309973001</v>
       </c>
       <c r="Q17">
-        <v>0.32652272963521312</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>33</v>
+        <v>0.3265227212947364</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C18">
-        <v>-3.5889921305602507E-2</v>
+        <v>-0.0358899358590011</v>
       </c>
       <c r="D18">
-        <v>-0.107997720390514</v>
+        <v>-0.1079977569941887</v>
       </c>
       <c r="E18">
-        <v>-7.032823334884393E-2</v>
+        <v>-0.07032821769318605</v>
       </c>
       <c r="F18">
-        <v>-0.1633927320141832</v>
+        <v>-0.1633928943247398</v>
       </c>
       <c r="G18">
-        <v>5.213144688068972E-2</v>
+        <v>0.05213098145023767</v>
       </c>
       <c r="H18">
-        <v>0.13112224326239369</v>
+        <v>0.1311222341995231</v>
       </c>
       <c r="I18">
-        <v>0.2028500417623452</v>
-      </c>
-      <c r="J18" s="4">
-        <v>0.29625420459944207</v>
+        <v>0.2028500459960807</v>
+      </c>
+      <c r="J18">
+        <v>0.2962542293911402</v>
       </c>
       <c r="K18">
-        <v>0.3681166031989177</v>
+        <v>0.3681166115250747</v>
       </c>
       <c r="L18">
-        <v>0.38499751014153488</v>
+        <v>0.3849976238106803</v>
       </c>
       <c r="M18">
-        <v>0.41289795375256272</v>
+        <v>0.4128980309945424</v>
       </c>
       <c r="N18">
-        <v>0.41309959910558208</v>
+        <v>0.4130996882925135</v>
       </c>
       <c r="O18">
-        <v>0.39085088343456859</v>
+        <v>0.3908509928614454</v>
       </c>
       <c r="P18">
-        <v>0.36249942283783221</v>
+        <v>0.3624995560060155</v>
       </c>
       <c r="Q18">
-        <v>0.34565935760167638</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>34</v>
+        <v>0.3456595280694555</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C19">
-        <v>-4.0152214407044577E-2</v>
+        <v>-0.04015222765520157</v>
       </c>
       <c r="D19">
-        <v>-0.1318489393411055</v>
+        <v>-0.1318489622486743</v>
       </c>
       <c r="E19">
-        <v>-7.7953506864173655E-2</v>
+        <v>-0.07795335237841323</v>
       </c>
       <c r="F19">
-        <v>-0.1316819857062777</v>
+        <v>-0.1316819810277096</v>
       </c>
       <c r="G19">
-        <v>0.1304797477702134</v>
+        <v>0.1304797238448181</v>
       </c>
       <c r="H19">
-        <v>0.19349662701618431</v>
+        <v>0.1934965996427603</v>
       </c>
       <c r="I19">
-        <v>0.26216180398487399</v>
-      </c>
-      <c r="J19" s="5">
-        <v>0.3444855488388131</v>
-      </c>
-      <c r="K19" s="3">
-        <v>0.39745030032694773</v>
+        <v>0.2621618002612146</v>
+      </c>
+      <c r="J19">
+        <v>0.3444855595896874</v>
+      </c>
+      <c r="K19">
+        <v>0.3974502960829567</v>
       </c>
       <c r="L19">
-        <v>0.41453804956747242</v>
+        <v>0.4145380737553177</v>
       </c>
       <c r="M19">
-        <v>0.43850863249032529</v>
+        <v>0.4385086584574193</v>
       </c>
       <c r="N19">
-        <v>0.43873406264921089</v>
+        <v>0.4387340901447844</v>
       </c>
       <c r="O19">
-        <v>0.42773025395201991</v>
+        <v>0.4277302789849836</v>
       </c>
       <c r="P19">
-        <v>0.43068483663476631</v>
+        <v>0.4306848683803703</v>
       </c>
       <c r="Q19">
-        <v>0.41881900010929829</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
+        <v>0.4188190609177476</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C20">
-        <v>-3.5195636678893999E-2</v>
+        <v>-0.03519564725124605</v>
       </c>
       <c r="D20">
-        <v>-0.13957264672104069</v>
+        <v>-0.1395727132852269</v>
       </c>
       <c r="E20">
-        <v>-0.1028179769966806</v>
+        <v>-0.1028179722307292</v>
       </c>
       <c r="F20">
-        <v>-1.1712305497346739E-2</v>
+        <v>-0.01171222316562659</v>
       </c>
       <c r="G20">
-        <v>0.1000906487641019</v>
+        <v>0.1000906344522332</v>
       </c>
       <c r="H20">
-        <v>0.13931036853648829</v>
+        <v>0.1393103781995562</v>
       </c>
       <c r="I20">
-        <v>0.23023520396283889</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0.31294985561472238</v>
-      </c>
-      <c r="K20" s="2">
-        <v>0.3503563973926313</v>
+        <v>0.2302352166207598</v>
+      </c>
+      <c r="J20">
+        <v>0.3129498916963588</v>
+      </c>
+      <c r="K20">
+        <v>0.3503564160215908</v>
       </c>
       <c r="L20">
-        <v>0.39472920756052088</v>
+        <v>0.3947292389696584</v>
       </c>
       <c r="M20">
-        <v>0.39644249111268132</v>
+        <v>0.3964424934389692</v>
       </c>
       <c r="N20">
-        <v>0.39775820783380678</v>
+        <v>0.397758210474633</v>
       </c>
       <c r="O20">
-        <v>0.44035117134252799</v>
+        <v>0.4403512004825024</v>
       </c>
       <c r="P20">
-        <v>0.43502267807654932</v>
+        <v>0.4350227366249557</v>
       </c>
       <c r="Q20">
-        <v>0.43177011580709268</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>36</v>
+        <v>0.4317701739158469</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C21">
-        <v>-2.4790219582243901E-2</v>
+        <v>-0.02479022766012359</v>
       </c>
       <c r="D21">
-        <v>-0.1908979540637355</v>
+        <v>-0.1908980310992313</v>
       </c>
       <c r="E21">
-        <v>-0.14170754928098181</v>
+        <v>-0.1417075340552505</v>
       </c>
       <c r="F21">
-        <v>-4.7074131621359198E-3</v>
+        <v>-0.004707533072251782</v>
       </c>
       <c r="G21">
-        <v>6.1399559960686842E-2</v>
+        <v>0.06139954904399974</v>
       </c>
       <c r="H21">
-        <v>9.0542858539730167E-2</v>
+        <v>0.09054284666348668</v>
       </c>
       <c r="I21">
-        <v>0.14736972272451909</v>
-      </c>
-      <c r="J21" s="2">
-        <v>0.18994400888017229</v>
+        <v>0.1473697679146884</v>
+      </c>
+      <c r="J21">
+        <v>0.1899440364463037</v>
       </c>
       <c r="K21">
-        <v>0.26514519264281261</v>
+        <v>0.2651452624326733</v>
       </c>
       <c r="L21">
-        <v>0.30042166369818218</v>
+        <v>0.3004217580538688</v>
       </c>
       <c r="M21">
-        <v>0.31538145233595261</v>
+        <v>0.31538159937374</v>
       </c>
       <c r="N21">
-        <v>0.29693922765172759</v>
+        <v>0.2969394408396574</v>
       </c>
       <c r="O21">
-        <v>0.25344429684264902</v>
+        <v>0.253444607914332</v>
       </c>
       <c r="P21">
-        <v>0.2330343164642858</v>
+        <v>0.2330347491351165</v>
       </c>
       <c r="Q21">
-        <v>0.24814010955127991</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>37</v>
+        <v>0.2481406084295581</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C22">
-        <v>-2.0201778673826248E-2</v>
+        <v>-0.02020178785206174</v>
       </c>
       <c r="D22">
-        <v>-0.17648996761647651</v>
+        <v>-0.1764900329451492</v>
       </c>
       <c r="E22">
-        <v>-0.13012102167370429</v>
+        <v>-0.1301210330034286</v>
       </c>
       <c r="F22">
-        <v>5.6077318984133553E-3</v>
+        <v>0.005607675150708944</v>
       </c>
       <c r="G22">
-        <v>5.880395185851095E-2</v>
+        <v>0.05880392878751975</v>
       </c>
       <c r="H22">
-        <v>8.237167958657457E-2</v>
+        <v>0.08237171549315728</v>
       </c>
       <c r="I22">
-        <v>0.1105367611429238</v>
-      </c>
-      <c r="J22" s="2">
-        <v>0.12775607113907969</v>
+        <v>0.1105367400586035</v>
+      </c>
+      <c r="J22">
+        <v>0.1277561962015523</v>
       </c>
       <c r="K22">
-        <v>0.20452745430320479</v>
+        <v>0.2045275609152642</v>
       </c>
       <c r="L22">
-        <v>0.24302740772863021</v>
+        <v>0.2430275371354803</v>
       </c>
       <c r="M22">
-        <v>0.25991302266106148</v>
+        <v>0.259913181252119</v>
       </c>
       <c r="N22">
-        <v>0.26813005296774439</v>
+        <v>0.2681303007598819</v>
       </c>
       <c r="O22">
-        <v>0.25102947173862988</v>
+        <v>0.2510298419119801</v>
       </c>
       <c r="P22">
-        <v>0.24958067232397629</v>
+        <v>0.2495811286896795</v>
       </c>
       <c r="Q22">
-        <v>0.24950853309087179</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>38</v>
+        <v>0.249509071249331</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C23">
-        <v>-4.1122705976330692E-2</v>
+        <v>-0.04112271602635775</v>
       </c>
       <c r="D23">
-        <v>-0.1536232167025561</v>
+        <v>-0.1536231916758719</v>
       </c>
       <c r="E23">
-        <v>-5.0856538421342343E-2</v>
+        <v>-0.05085659668158687</v>
       </c>
       <c r="F23">
-        <v>7.0759247221637428E-2</v>
+        <v>0.07075925478408648</v>
       </c>
       <c r="G23">
-        <v>0.2087219756706413</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0.30275152934932181</v>
+        <v>0.2087219382591486</v>
+      </c>
+      <c r="H23">
+        <v>0.302751498239957</v>
       </c>
       <c r="I23">
-        <v>0.3365893813770543</v>
+        <v>0.3365893985938779</v>
       </c>
       <c r="J23">
-        <v>0.34926963155199409</v>
+        <v>0.3492696882435123</v>
       </c>
       <c r="K23">
-        <v>0.37143979460726101</v>
+        <v>0.3714398931616508</v>
       </c>
       <c r="L23">
-        <v>0.36919242317369277</v>
+        <v>0.3691926591426595</v>
       </c>
       <c r="M23">
-        <v>0.36023852597998202</v>
+        <v>0.3602388536717347</v>
       </c>
       <c r="N23">
-        <v>0.34620178983156003</v>
+        <v>0.3462022204111478</v>
       </c>
       <c r="O23">
-        <v>0.34138889844584303</v>
+        <v>0.3413893553778251</v>
       </c>
       <c r="P23">
-        <v>0.33785996925799883</v>
+        <v>0.3378604610403103</v>
       </c>
       <c r="Q23">
-        <v>0.31562063979240113</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>39</v>
+        <v>0.3156210636228819</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C24">
-        <v>-6.7037821502683517E-2</v>
+        <v>-0.06703782328052853</v>
       </c>
       <c r="D24">
-        <v>-0.1211297380930431</v>
+        <v>-0.1211296747792485</v>
       </c>
       <c r="E24">
-        <v>-0.17473235489378669</v>
+        <v>-0.174732366058242</v>
       </c>
       <c r="F24">
-        <v>-0.13884512127843049</v>
+        <v>-0.138845048150769</v>
       </c>
       <c r="G24">
-        <v>-0.11882376820735351</v>
+        <v>-0.1188236691198624</v>
       </c>
       <c r="H24">
-        <v>-6.5066392197234285E-2</v>
+        <v>-0.06506638183920394</v>
       </c>
       <c r="I24">
-        <v>-0.11443860085593729</v>
+        <v>-0.1144386190318406</v>
       </c>
       <c r="J24">
-        <v>-6.0516531396052543E-2</v>
-      </c>
-      <c r="K24" s="2">
-        <v>9.0520078037308577E-2</v>
+        <v>-0.06051652353280809</v>
+      </c>
+      <c r="K24">
+        <v>0.09052013271832064</v>
       </c>
       <c r="L24">
-        <v>0.19273077200024141</v>
+        <v>0.1927308485671519</v>
       </c>
       <c r="M24">
-        <v>0.22657146651340779</v>
+        <v>0.2265715952858876</v>
       </c>
       <c r="N24">
-        <v>0.20167201937817369</v>
+        <v>0.2016722802986669</v>
       </c>
       <c r="O24">
-        <v>0.13898333446254771</v>
+        <v>0.1389837187767936</v>
       </c>
       <c r="P24">
-        <v>7.6363376262435889E-2</v>
+        <v>0.0763638391195474</v>
       </c>
       <c r="Q24">
-        <v>-5.4217166748831754E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>40</v>
+        <v>-0.00542113439628579</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C25">
-        <v>-6.9168112258287159E-2</v>
+        <v>-0.06916812452951064</v>
       </c>
       <c r="D25">
-        <v>-0.12723025468056359</v>
+        <v>-0.1272302024566438</v>
       </c>
       <c r="E25">
-        <v>-0.18667424921330031</v>
+        <v>-0.1866742570873561</v>
       </c>
       <c r="F25">
-        <v>-0.14134548534711869</v>
+        <v>-0.1413455025395035</v>
       </c>
       <c r="G25">
-        <v>-0.1130199697290044</v>
+        <v>-0.1130199263032779</v>
       </c>
       <c r="H25">
-        <v>-0.1051298116416808</v>
+        <v>-0.1051298086670136</v>
       </c>
       <c r="I25">
-        <v>-0.20205735691453741</v>
+        <v>-0.2020573292517668</v>
       </c>
       <c r="J25">
-        <v>-0.1322392797236939</v>
+        <v>-0.1322391942892999</v>
       </c>
       <c r="K25">
-        <v>-5.1218294655323522E-2</v>
-      </c>
-      <c r="L25" s="2">
-        <v>0.15254965903773199</v>
+        <v>-0.05121822662319753</v>
+      </c>
+      <c r="L25">
+        <v>0.1525497356999497</v>
       </c>
       <c r="M25">
-        <v>0.18120652857560579</v>
+        <v>0.181206617490755</v>
       </c>
       <c r="N25">
-        <v>0.1967348248035766</v>
+        <v>0.1967350065837511</v>
       </c>
       <c r="O25">
-        <v>0.16659725145039689</v>
+        <v>0.1665975405781145</v>
       </c>
       <c r="P25">
-        <v>0.1153935420798107</v>
+        <v>0.1153939563488645</v>
       </c>
       <c r="Q25">
-        <v>4.3003357856149567E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>41</v>
+        <v>0.04300384961437537</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C26">
-        <v>-6.9967703104700477E-2</v>
+        <v>-0.06996770607470938</v>
       </c>
       <c r="D26">
-        <v>-0.13866945590639379</v>
+        <v>-0.1386694206906601</v>
       </c>
       <c r="E26">
-        <v>-0.14920280475908321</v>
+        <v>-0.1492028120212948</v>
       </c>
       <c r="F26">
-        <v>-9.294768280101677E-2</v>
+        <v>-0.09294772737637018</v>
       </c>
       <c r="G26">
-        <v>-0.13484320116106219</v>
+        <v>-0.1348431777581715</v>
       </c>
       <c r="H26">
-        <v>-9.5581128280556149E-2</v>
+        <v>-0.09558114469268535</v>
       </c>
       <c r="I26">
-        <v>1.564010526320719E-2</v>
+        <v>0.0156401218864985</v>
       </c>
       <c r="J26">
-        <v>-4.7254081067588397E-2</v>
-      </c>
-      <c r="K26" s="2">
-        <v>8.9585595702724202E-2</v>
+        <v>-0.04725405969501857</v>
+      </c>
+      <c r="K26">
+        <v>0.08958577253139713</v>
       </c>
       <c r="L26">
-        <v>0.17305619337912659</v>
+        <v>0.1730562532235956</v>
       </c>
       <c r="M26">
-        <v>0.18497572168862009</v>
+        <v>0.184975827997342</v>
       </c>
       <c r="N26">
-        <v>0.16341194899637659</v>
+        <v>0.1634121781909894</v>
       </c>
       <c r="O26">
-        <v>0.1290106641845031</v>
+        <v>0.1290109861759524</v>
       </c>
       <c r="P26">
-        <v>6.5155448331074992E-2</v>
+        <v>0.06515588884019548</v>
       </c>
       <c r="Q26">
-        <v>-2.1898876257478259E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>42</v>
+        <v>-0.02189833335170206</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C27">
-        <v>-6.8357226924847039E-2</v>
+        <v>-0.06835723524644902</v>
       </c>
       <c r="D27">
-        <v>-0.1218033043094682</v>
+        <v>-0.1218032679635069</v>
       </c>
       <c r="E27">
-        <v>-0.13260639866768509</v>
+        <v>-0.1326064262611217</v>
       </c>
       <c r="F27">
-        <v>-7.4347437975750857E-2</v>
+        <v>-0.07434741830302222</v>
       </c>
       <c r="G27">
-        <v>-0.1089463426233238</v>
+        <v>-0.108946305541049</v>
       </c>
       <c r="H27">
-        <v>-7.7168383845713479E-2</v>
+        <v>-0.07716839116726076</v>
       </c>
       <c r="I27">
-        <v>1.5300630864306939E-2</v>
+        <v>0.01530064310537916</v>
       </c>
       <c r="J27">
-        <v>-3.4961591454740017E-2</v>
+        <v>-0.03496155532447826</v>
       </c>
       <c r="K27">
-        <v>7.018399505714841E-2</v>
-      </c>
-      <c r="L27" s="2">
-        <v>0.19732319792215089</v>
+        <v>0.07018400143184858</v>
+      </c>
+      <c r="L27">
+        <v>0.1973232367823628</v>
       </c>
       <c r="M27">
-        <v>0.25971101946596481</v>
+        <v>0.2597110696264704</v>
       </c>
       <c r="N27">
-        <v>0.27815800703373778</v>
+        <v>0.2781581129129101</v>
       </c>
       <c r="O27">
-        <v>0.3000346899826839</v>
+        <v>0.3000348089575787</v>
       </c>
       <c r="P27">
-        <v>0.27447383799959452</v>
+        <v>0.2744739818288325</v>
       </c>
       <c r="Q27">
-        <v>0.26544946386296842</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
+        <v>0.2654496130590285</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C28">
-        <v>-6.7788499615906425E-2</v>
+        <v>-0.06778850061997381</v>
       </c>
       <c r="D28">
-        <v>-0.1203297310582382</v>
+        <v>-0.1203296807312537</v>
       </c>
       <c r="E28">
-        <v>-0.17575414073977019</v>
+        <v>-0.1757541487566273</v>
       </c>
       <c r="F28">
-        <v>-0.13172531177276631</v>
+        <v>-0.1317253162035598</v>
       </c>
       <c r="G28">
-        <v>-0.10985350312049159</v>
+        <v>-0.1098534934903973</v>
       </c>
       <c r="H28">
-        <v>-9.4137034234342304E-2</v>
+        <v>-0.09413706630609424</v>
       </c>
       <c r="I28">
-        <v>-0.1588849826187268</v>
+        <v>-0.1588849626005718</v>
       </c>
       <c r="J28">
-        <v>-0.1422836515198703</v>
+        <v>-0.1422836447672932</v>
       </c>
       <c r="K28">
-        <v>-7.3565555083535988E-2</v>
-      </c>
-      <c r="L28" s="2">
-        <v>0.15358273934536179</v>
+        <v>-0.07356555546681164</v>
+      </c>
+      <c r="L28">
+        <v>0.1535827872467249</v>
       </c>
       <c r="M28">
-        <v>0.19857302750709641</v>
+        <v>0.1985730857640546</v>
       </c>
       <c r="N28">
-        <v>0.23244717161688561</v>
+        <v>0.2324472447119101</v>
       </c>
       <c r="O28">
-        <v>0.24315706019877739</v>
+        <v>0.2431571398585742</v>
       </c>
       <c r="P28">
-        <v>0.24847264267259631</v>
+        <v>0.248472741853708</v>
       </c>
       <c r="Q28">
-        <v>0.2471674000982256</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>44</v>
+        <v>0.2471675343541554</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C29">
-        <v>-6.925493458772479E-2</v>
+        <v>-0.06925495177977756</v>
       </c>
       <c r="D29">
-        <v>-0.1279818857470762</v>
+        <v>-0.1279818448728843</v>
       </c>
       <c r="E29">
-        <v>-0.18313492071244089</v>
+        <v>-0.1831349229621832</v>
       </c>
       <c r="F29">
-        <v>-0.1362695655210632</v>
+        <v>-0.1362694570912125</v>
       </c>
       <c r="G29">
-        <v>-0.110480903108924</v>
+        <v>-0.1104807519067014</v>
       </c>
       <c r="H29">
-        <v>-8.8331668426214482E-2</v>
+        <v>-0.08833166710935411</v>
       </c>
       <c r="I29">
-        <v>-0.15081693138798791</v>
+        <v>-0.150816902895071</v>
       </c>
       <c r="J29">
-        <v>-0.1195011097052926</v>
+        <v>-0.1195010907395122</v>
       </c>
       <c r="K29">
-        <v>-6.3579036329465669E-2</v>
-      </c>
-      <c r="L29" s="2">
-        <v>0.15382325361070809</v>
+        <v>-0.06357896503416866</v>
+      </c>
+      <c r="L29">
+        <v>0.153823296911967</v>
       </c>
       <c r="M29">
-        <v>0.20355288903853169</v>
+        <v>0.203552944237636</v>
       </c>
       <c r="N29">
-        <v>0.24111514094010611</v>
+        <v>0.2411152056284352</v>
       </c>
       <c r="O29">
-        <v>0.25437547277563688</v>
+        <v>0.2543755378078262</v>
       </c>
       <c r="P29">
-        <v>0.26751181157699078</v>
+        <v>0.2675119201233639</v>
       </c>
       <c r="Q29">
-        <v>0.26772437543376959</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>45</v>
+        <v>0.267724502292757</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C30">
-        <v>-6.9867133635566417E-2</v>
+        <v>-0.06986714284236778</v>
       </c>
       <c r="D30">
-        <v>-0.1258406834585642</v>
+        <v>-0.125840644779348</v>
       </c>
       <c r="E30">
-        <v>-0.1791152496232761</v>
+        <v>-0.1791152539058423</v>
       </c>
       <c r="F30">
-        <v>-0.13543572287393171</v>
+        <v>-0.135435749943636</v>
       </c>
       <c r="G30">
-        <v>-0.1174432106078393</v>
+        <v>-0.1174431941075682</v>
       </c>
       <c r="H30">
-        <v>-9.8552998377280168E-2</v>
+        <v>-0.09855299707849108</v>
       </c>
       <c r="I30">
-        <v>-0.15860657508985229</v>
+        <v>-0.1586065716259277</v>
       </c>
       <c r="J30">
-        <v>-0.13420445951025239</v>
+        <v>-0.1342044427127409</v>
       </c>
       <c r="K30">
-        <v>-7.8299448088702095E-2</v>
-      </c>
-      <c r="L30" s="2">
-        <v>0.1336209992746534</v>
+        <v>-0.07829942716416073</v>
+      </c>
+      <c r="L30">
+        <v>0.1336210479950345</v>
       </c>
       <c r="M30">
-        <v>0.18789183928544101</v>
+        <v>0.1878918966052032</v>
       </c>
       <c r="N30">
-        <v>0.21984521044118391</v>
+        <v>0.2198452911463512</v>
       </c>
       <c r="O30">
-        <v>0.2472860650449008</v>
+        <v>0.2472861329324014</v>
       </c>
       <c r="P30">
-        <v>0.26250541047613968</v>
+        <v>0.2625055167108208</v>
       </c>
       <c r="Q30">
-        <v>0.27310326082877079</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>46</v>
+        <v>0.273103388802371</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C31">
-        <v>-6.9208123815460779E-2</v>
+        <v>-0.06920814097317245</v>
       </c>
       <c r="D31">
-        <v>-0.1202151018858995</v>
+        <v>-0.1202150548829224</v>
       </c>
       <c r="E31">
-        <v>-0.17553946266251719</v>
+        <v>-0.1755396761108658</v>
       </c>
       <c r="F31">
-        <v>-0.13114231167906709</v>
+        <v>-0.1311423245381234</v>
       </c>
       <c r="G31">
-        <v>-0.1107378785386781</v>
+        <v>-0.1107378800158826</v>
       </c>
       <c r="H31">
-        <v>-9.1418656550493277E-2</v>
+        <v>-0.09141865624514606</v>
       </c>
       <c r="I31">
-        <v>-0.15959087018148541</v>
+        <v>-0.1595908501278024</v>
       </c>
       <c r="J31">
-        <v>-0.13091928091056609</v>
+        <v>-0.1309192439477382</v>
       </c>
       <c r="K31">
-        <v>-8.2684691395821394E-2</v>
-      </c>
-      <c r="L31" s="2">
-        <v>0.1078901359590346</v>
+        <v>-0.08268459468778368</v>
+      </c>
+      <c r="L31">
+        <v>0.1078901866203007</v>
       </c>
       <c r="M31">
-        <v>0.17177194327710721</v>
+        <v>0.1717719953140199</v>
       </c>
       <c r="N31">
-        <v>0.208001370672215</v>
+        <v>0.208001441236665</v>
       </c>
       <c r="O31">
-        <v>0.23620312643450339</v>
+        <v>0.2362031305314399</v>
       </c>
       <c r="P31">
-        <v>0.25414912691902919</v>
+        <v>0.2541491831657866</v>
       </c>
       <c r="Q31">
-        <v>0.28030337809209571</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>47</v>
+        <v>0.2803034470684014</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C32">
-        <v>-6.6995635784906346E-2</v>
+        <v>-0.06699563789458877</v>
       </c>
       <c r="D32">
-        <v>-0.1257774030819282</v>
+        <v>-0.1257773315319022</v>
       </c>
       <c r="E32">
-        <v>-0.18129848777895749</v>
+        <v>-0.1812985130115815</v>
       </c>
       <c r="F32">
-        <v>-0.14016834298659811</v>
+        <v>-0.1401682849199772</v>
       </c>
       <c r="G32">
-        <v>-0.1129361239181494</v>
+        <v>-0.1129360819585564</v>
       </c>
       <c r="H32">
-        <v>-9.4631465807572757E-2</v>
+        <v>-0.09463143327283859</v>
       </c>
       <c r="I32">
-        <v>-0.16649648273464659</v>
+        <v>-0.1664964710770554</v>
       </c>
       <c r="J32">
-        <v>-0.12837550526124489</v>
+        <v>-0.1283754939654969</v>
       </c>
       <c r="K32">
-        <v>-6.8908150038546209E-2</v>
-      </c>
-      <c r="L32" s="2">
-        <v>0.14818952138598071</v>
+        <v>-0.0689081262771543</v>
+      </c>
+      <c r="L32">
+        <v>0.1481895759911803</v>
       </c>
       <c r="M32">
-        <v>0.199846088972367</v>
+        <v>0.1998461564798459</v>
       </c>
       <c r="N32">
-        <v>0.226295325971752</v>
+        <v>0.2262954122287865</v>
       </c>
       <c r="O32">
-        <v>0.22805723413874951</v>
+        <v>0.2280573575861646</v>
       </c>
       <c r="P32">
-        <v>0.20951668968739021</v>
+        <v>0.2095168546241163</v>
       </c>
       <c r="Q32">
-        <v>0.18849092799032069</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>48</v>
+        <v>0.1884911457061462</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C33">
-        <v>-6.6346068199675132E-2</v>
+        <v>-0.06634607060514364</v>
       </c>
       <c r="D33">
-        <v>-0.1205868622120467</v>
+        <v>-0.1205868115716428</v>
       </c>
       <c r="E33">
-        <v>-0.1751445221087502</v>
+        <v>-0.1751445365732879</v>
       </c>
       <c r="F33">
-        <v>-0.12853158198751</v>
+        <v>-0.1285315426511476</v>
       </c>
       <c r="G33">
-        <v>-0.10575579306626599</v>
+        <v>-0.1057557375555377</v>
       </c>
       <c r="H33">
-        <v>-8.7415772449075946E-2</v>
+        <v>-0.08741576479684017</v>
       </c>
       <c r="I33">
-        <v>-0.16249240982362839</v>
+        <v>-0.1624924174197062</v>
       </c>
       <c r="J33">
-        <v>-0.12271491902008939</v>
+        <v>-0.1227149067031206</v>
       </c>
       <c r="K33">
-        <v>-6.0080294316644037E-2</v>
-      </c>
-      <c r="L33" s="2">
-        <v>0.15360951965428599</v>
+        <v>-0.06008031336166681</v>
+      </c>
+      <c r="L33">
+        <v>0.153609568745792</v>
       </c>
       <c r="M33">
-        <v>0.19618492753100869</v>
+        <v>0.1961849821536709</v>
       </c>
       <c r="N33">
-        <v>0.22914068900599899</v>
+        <v>0.2291407667512251</v>
       </c>
       <c r="O33">
-        <v>0.23597907536953761</v>
+        <v>0.235979153140922</v>
       </c>
       <c r="P33">
-        <v>0.2296745673259791</v>
+        <v>0.229674684921128</v>
       </c>
       <c r="Q33">
-        <v>0.21554769082473249</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>49</v>
+        <v>0.2155478616287634</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C34">
-        <v>-6.5478810606256183E-2</v>
+        <v>-0.06547881397945761</v>
       </c>
       <c r="D34">
-        <v>-0.12381593451444819</v>
+        <v>-0.1238158864382878</v>
       </c>
       <c r="E34">
-        <v>-0.17923078634830411</v>
+        <v>-0.1792307978627014</v>
       </c>
       <c r="F34">
-        <v>-0.13966845047474219</v>
+        <v>-0.1396684212908147</v>
       </c>
       <c r="G34">
-        <v>-0.11447911175867891</v>
+        <v>-0.1144790954555627</v>
       </c>
       <c r="H34">
-        <v>-9.5975212873211285E-2</v>
+        <v>-0.09597521222755559</v>
       </c>
       <c r="I34">
-        <v>-0.1597843244855669</v>
+        <v>-0.1597843105690667</v>
       </c>
       <c r="J34">
-        <v>-0.13977554382902749</v>
+        <v>-0.1397755257287259</v>
       </c>
       <c r="K34">
-        <v>-7.7066974184765991E-2</v>
-      </c>
-      <c r="L34" s="2">
-        <v>0.13451301773905949</v>
+        <v>-0.07706695305687362</v>
+      </c>
+      <c r="L34">
+        <v>0.1345130736521991</v>
       </c>
       <c r="M34">
-        <v>0.19025318544556019</v>
+        <v>0.1902532484206867</v>
       </c>
       <c r="N34">
-        <v>0.22033781393516649</v>
+        <v>0.2203378881601879</v>
       </c>
       <c r="O34">
-        <v>0.23261019601306929</v>
+        <v>0.2326102849382576</v>
       </c>
       <c r="P34">
-        <v>0.22734587441141821</v>
+        <v>0.2273460007856048</v>
       </c>
       <c r="Q34">
-        <v>0.21607017930425901</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>50</v>
+        <v>0.2160703219104417</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C35">
-        <v>-7.1347264886246861E-2</v>
+        <v>-0.07134727666295611</v>
       </c>
       <c r="D35">
-        <v>-0.13413224594931039</v>
+        <v>-0.1341321966547849</v>
       </c>
       <c r="E35">
-        <v>-0.18659202980902309</v>
+        <v>-0.1865920468517542</v>
       </c>
       <c r="F35">
-        <v>-0.14299361790365001</v>
+        <v>-0.1429936051316575</v>
       </c>
       <c r="G35">
-        <v>-0.12110571770162119</v>
+        <v>-0.1211057185929193</v>
       </c>
       <c r="H35">
-        <v>-0.10529732385209629</v>
+        <v>-0.1052973233232974</v>
       </c>
       <c r="I35">
-        <v>-0.17246063812549031</v>
+        <v>-0.172460620987936</v>
       </c>
       <c r="J35">
-        <v>-0.14522860353221009</v>
+        <v>-0.145228593994999</v>
       </c>
       <c r="K35">
-        <v>-8.315190743135252E-2</v>
-      </c>
-      <c r="L35" s="2">
-        <v>0.1269899538524456</v>
+        <v>-0.08315187129805092</v>
+      </c>
+      <c r="L35">
+        <v>0.1269900004904863</v>
       </c>
       <c r="M35">
-        <v>0.17194448095013359</v>
+        <v>0.1719445414290377</v>
       </c>
       <c r="N35">
-        <v>0.21030375769927909</v>
+        <v>0.2103038228794485</v>
       </c>
       <c r="O35">
-        <v>0.228873348113006</v>
+        <v>0.228873423921861</v>
       </c>
       <c r="P35">
-        <v>0.22895077469241301</v>
+        <v>0.2289508775952245</v>
       </c>
       <c r="Q35">
-        <v>0.22623103359394431</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>51</v>
+        <v>0.2262311672637202</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C36">
-        <v>-6.5952331535988465E-2</v>
+        <v>-0.06595233782282574</v>
       </c>
       <c r="D36">
-        <v>-0.12585013932801989</v>
+        <v>-0.1258500987171619</v>
       </c>
       <c r="E36">
-        <v>-0.178952125008636</v>
+        <v>-0.1789521416520456</v>
       </c>
       <c r="F36">
-        <v>-0.1296427963328724</v>
+        <v>-0.1296428080890227</v>
       </c>
       <c r="G36">
-        <v>-0.1099447372623515</v>
+        <v>-0.109944682910228</v>
       </c>
       <c r="H36">
-        <v>-9.1635326612509282E-2</v>
+        <v>-0.09163528390619734</v>
       </c>
       <c r="I36">
-        <v>-0.13877267267771901</v>
+        <v>-0.1387726670685099</v>
       </c>
       <c r="J36">
-        <v>-0.1176623650850316</v>
+        <v>-0.1176623482560764</v>
       </c>
       <c r="K36">
-        <v>-6.3915791716989592E-2</v>
-      </c>
-      <c r="L36" s="2">
-        <v>0.100162807668013</v>
+        <v>-0.06391576652905398</v>
+      </c>
+      <c r="L36">
+        <v>0.1001628608597748</v>
       </c>
       <c r="M36">
-        <v>0.17423404614360141</v>
+        <v>0.1742341130795909</v>
       </c>
       <c r="N36">
-        <v>0.20829267995699241</v>
+        <v>0.2082927504979321</v>
       </c>
       <c r="O36">
-        <v>0.2392308209042126</v>
+        <v>0.2392308805159678</v>
       </c>
       <c r="P36">
-        <v>0.2451761874261115</v>
+        <v>0.2451762595524367</v>
       </c>
       <c r="Q36">
-        <v>0.27197591756875772</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>52</v>
+        <v>0.2719760224355917</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C37">
-        <v>-0.11314841908058609</v>
+        <v>-0.1131483890117223</v>
       </c>
       <c r="D37">
-        <v>-0.18461026284053039</v>
+        <v>-0.1846102206715545</v>
       </c>
       <c r="E37">
-        <v>-0.1132089283984192</v>
+        <v>-0.1132089231051114</v>
       </c>
       <c r="F37">
-        <v>-2.634164952313435E-2</v>
+        <v>-0.02634170133051322</v>
       </c>
       <c r="G37">
-        <v>-8.1310458828502949E-2</v>
+        <v>-0.08131043078530781</v>
       </c>
       <c r="H37">
-        <v>-2.659456159423049E-2</v>
+        <v>-0.02659449792678032</v>
       </c>
       <c r="I37">
-        <v>7.0115015798232219E-2</v>
+        <v>0.07011522671068954</v>
       </c>
       <c r="J37">
-        <v>0.1027445526995107</v>
+        <v>0.1027448089343328</v>
       </c>
       <c r="K37">
-        <v>9.3239678595555306E-2</v>
+        <v>0.09323991787350003</v>
       </c>
       <c r="L37">
-        <v>9.7469245515093048E-2</v>
+        <v>0.09746953042696342</v>
       </c>
       <c r="M37">
-        <v>8.3002397072095876E-2</v>
+        <v>0.08300274769097792</v>
       </c>
       <c r="N37">
-        <v>4.0433215464465593E-2</v>
+        <v>0.04043360844010348</v>
       </c>
       <c r="O37">
-        <v>6.8211537433813987E-2</v>
+        <v>0.06821210974230467</v>
       </c>
       <c r="P37">
-        <v>7.1900083490852945E-2</v>
+        <v>0.07190089116873812</v>
       </c>
       <c r="Q37">
-        <v>7.4831741125298681E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>53</v>
+        <v>0.07483279016171375</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C38">
-        <v>-8.9226837138832837E-2</v>
+        <v>-0.08922681817711157</v>
       </c>
       <c r="D38">
-        <v>-0.1713105567637255</v>
+        <v>-0.1713105641321211</v>
       </c>
       <c r="E38">
-        <v>-0.14544493790042509</v>
+        <v>-0.1454451691945838</v>
       </c>
       <c r="F38">
-        <v>-1.144965434834171E-2</v>
+        <v>-0.01144965368458345</v>
       </c>
       <c r="G38">
-        <v>1.0498748906429141E-2</v>
+        <v>0.01049873571120314</v>
       </c>
       <c r="H38">
-        <v>0.1442370850776527</v>
-      </c>
-      <c r="I38" s="2">
-        <v>0.2775675146089806</v>
+        <v>0.1442370860760197</v>
+      </c>
+      <c r="I38">
+        <v>0.2775675924192159</v>
       </c>
       <c r="J38">
-        <v>0.26757450541673611</v>
+        <v>0.2675740167008404</v>
       </c>
       <c r="K38">
-        <v>0.22444575173848491</v>
+        <v>0.2244458655513419</v>
       </c>
       <c r="L38">
-        <v>0.18226281402768921</v>
+        <v>0.1822629921309987</v>
       </c>
       <c r="M38">
-        <v>0.18220114204189711</v>
+        <v>0.1822013599621413</v>
       </c>
       <c r="N38">
-        <v>0.16386215651528191</v>
+        <v>0.1638623443203118</v>
       </c>
       <c r="O38">
-        <v>0.16523474019553991</v>
+        <v>0.1652348749995521</v>
       </c>
       <c r="P38">
-        <v>0.18303504876808621</v>
+        <v>0.1830352617127707</v>
       </c>
       <c r="Q38">
-        <v>0.196992134001686</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>54</v>
+        <v>0.1969924062293565</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C39">
-        <v>-8.3528659657616425E-2</v>
+        <v>-0.08352863548793392</v>
       </c>
       <c r="D39">
-        <v>-0.1500533259893084</v>
+        <v>-0.1500533043058006</v>
       </c>
       <c r="E39">
-        <v>-0.117167995271697</v>
+        <v>-0.1171681536130343</v>
       </c>
       <c r="F39">
-        <v>7.1627543799385783E-3</v>
+        <v>0.007162827723015588</v>
       </c>
       <c r="G39">
-        <v>2.0566796750604459E-2</v>
-      </c>
-      <c r="H39" s="2">
-        <v>0.1238650501950322</v>
+        <v>0.02056691139874839</v>
+      </c>
+      <c r="H39">
+        <v>0.1238650615993945</v>
       </c>
       <c r="I39">
-        <v>0.24515856695666949</v>
+        <v>0.2451585551749226</v>
       </c>
       <c r="J39">
-        <v>0.23715032466795261</v>
+        <v>0.2371503086710819</v>
       </c>
       <c r="K39">
-        <v>0.25029905760195448</v>
+        <v>0.2502992161671181</v>
       </c>
       <c r="L39">
-        <v>0.2356809172994391</v>
+        <v>0.2356810425067031</v>
       </c>
       <c r="M39">
-        <v>0.22068664496770099</v>
+        <v>0.2206868086997163</v>
       </c>
       <c r="N39">
-        <v>0.23839279331835991</v>
+        <v>0.2383929872901125</v>
       </c>
       <c r="O39">
-        <v>0.22498494970686131</v>
+        <v>0.2249851612206127</v>
       </c>
       <c r="P39">
-        <v>0.21362124862329609</v>
+        <v>0.2136215224360192</v>
       </c>
       <c r="Q39">
-        <v>0.21482441780216691</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>55</v>
+        <v>0.214824737513282</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C40">
-        <v>-0.11661024487017389</v>
+        <v>-0.1166102213689711</v>
       </c>
       <c r="D40">
-        <v>-8.1966766744247882E-2</v>
+        <v>-0.08196674127859117</v>
       </c>
       <c r="E40">
-        <v>-3.9481700469426919E-3</v>
+        <v>-0.003948187674663464</v>
       </c>
       <c r="F40">
-        <v>-3.2925514391594933E-2</v>
-      </c>
-      <c r="G40" s="2">
-        <v>9.1072753435794296E-2</v>
+        <v>-0.0329255137539</v>
+      </c>
+      <c r="G40">
+        <v>0.0910728027405954</v>
       </c>
       <c r="H40">
-        <v>0.15588100703969129</v>
+        <v>0.1558810675932878</v>
       </c>
       <c r="I40">
-        <v>0.15489885112216401</v>
+        <v>0.154898983108593</v>
       </c>
       <c r="J40">
-        <v>0.1130362057577257</v>
+        <v>0.1130364296342557</v>
       </c>
       <c r="K40">
-        <v>0.10726051572115999</v>
+        <v>0.1072607806464426</v>
       </c>
       <c r="L40">
-        <v>0.14335305667957041</v>
+        <v>0.1433533385407892</v>
       </c>
       <c r="M40">
-        <v>0.13789721647859929</v>
+        <v>0.1378974914695875</v>
       </c>
       <c r="N40">
-        <v>0.15886491830936661</v>
+        <v>0.158865237857644</v>
       </c>
       <c r="O40">
-        <v>0.14132269101058009</v>
+        <v>0.1413231711570659</v>
       </c>
       <c r="P40">
-        <v>0.1100970986740491</v>
+        <v>0.1100977313958577</v>
       </c>
       <c r="Q40">
-        <v>4.8130582253516963E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>56</v>
+        <v>0.04813141218072734</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C41">
-        <v>-0.1235405999514196</v>
+        <v>-0.1235406416230714</v>
       </c>
       <c r="D41">
-        <v>-0.28052814749204003</v>
+        <v>-0.2805281271923571</v>
       </c>
       <c r="E41">
-        <v>-0.18997653962224459</v>
+        <v>-0.1899765346941214</v>
       </c>
       <c r="F41">
-        <v>-0.18660092583652599</v>
+        <v>-0.1866009110718286</v>
       </c>
       <c r="G41">
-        <v>-0.11112017287628589</v>
+        <v>-0.1111201695349294</v>
       </c>
       <c r="H41">
-        <v>-9.0492564931809724E-2</v>
+        <v>-0.09049252790580412</v>
       </c>
       <c r="I41">
-        <v>-6.7135748907148782E-2</v>
+        <v>-0.06713571981137348</v>
       </c>
       <c r="J41">
-        <v>-1.8675278563536419E-2</v>
+        <v>-0.01867524091282766</v>
       </c>
       <c r="K41">
-        <v>-4.800443550544374E-2</v>
+        <v>-0.04800443365617773</v>
       </c>
       <c r="L41">
-        <v>-8.4198630505543048E-2</v>
+        <v>-0.08419846116465404</v>
       </c>
       <c r="M41">
-        <v>-7.3439615843409481E-2</v>
+        <v>-0.07343945100687635</v>
       </c>
       <c r="N41">
-        <v>-9.6631210210212731E-2</v>
+        <v>-0.09663095114024138</v>
       </c>
       <c r="O41">
-        <v>-0.15650709797987769</v>
+        <v>-0.1565068147909036</v>
       </c>
       <c r="P41">
-        <v>-0.16569907969029851</v>
+        <v>-0.1656987887925211</v>
       </c>
       <c r="Q41">
-        <v>-0.182050892754022</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>57</v>
+        <v>-0.1820505651773815</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C42">
-        <v>-2.2890052509304759E-2</v>
+        <v>-0.02289006013049057</v>
       </c>
       <c r="D42">
-        <v>-0.3114616594391908</v>
+        <v>-0.3114617325522749</v>
       </c>
       <c r="E42">
-        <v>-0.17910916306563049</v>
+        <v>-0.1791092067782892</v>
       </c>
       <c r="F42">
-        <v>5.1333041460466057E-2</v>
+        <v>0.05133308787975923</v>
       </c>
       <c r="G42">
-        <v>0.12615840611262699</v>
-      </c>
-      <c r="H42" s="2">
-        <v>0.16633414527963919</v>
+        <v>0.1261584015520006</v>
+      </c>
+      <c r="H42">
+        <v>0.1663341742391158</v>
       </c>
       <c r="I42">
-        <v>0.25145587147385923</v>
+        <v>0.2514558978103125</v>
       </c>
       <c r="J42">
-        <v>0.26455859170394991</v>
+        <v>0.2645586176128985</v>
       </c>
       <c r="K42">
-        <v>0.24257189264877169</v>
+        <v>0.2425719448513322</v>
       </c>
       <c r="L42">
-        <v>0.26909331928317182</v>
+        <v>0.26909344746004</v>
       </c>
       <c r="M42">
-        <v>0.26795261822349831</v>
+        <v>0.2679527295358385</v>
       </c>
       <c r="N42">
-        <v>0.24592209556783459</v>
+        <v>0.2459222550825768</v>
       </c>
       <c r="O42">
-        <v>0.23677739076381149</v>
+        <v>0.236777584879103</v>
       </c>
       <c r="P42">
-        <v>0.2376222746998316</v>
+        <v>0.2376225030262258</v>
       </c>
       <c r="Q42">
-        <v>0.22433337204694531</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>58</v>
+        <v>0.2243336282059194</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C43">
-        <v>-6.7061822434962656E-2</v>
+        <v>-0.06706186327913065</v>
       </c>
       <c r="D43">
-        <v>-0.11312176862108041</v>
+        <v>-0.1131217719135165</v>
       </c>
       <c r="E43">
-        <v>-2.7095629536232731E-2</v>
+        <v>-0.0270956301588963</v>
       </c>
       <c r="F43">
-        <v>1.7182183855057782E-2</v>
-      </c>
-      <c r="G43" s="2">
-        <v>0.1720585570423491</v>
+        <v>0.01718215582788961</v>
+      </c>
+      <c r="G43">
+        <v>0.1720585727042078</v>
       </c>
       <c r="H43">
-        <v>0.22219006026362381</v>
+        <v>0.2221899955954542</v>
       </c>
       <c r="I43">
-        <v>0.25294254787862208</v>
+        <v>0.2529425444946322</v>
       </c>
       <c r="J43">
-        <v>0.23574792308444331</v>
+        <v>0.235747941839604</v>
       </c>
       <c r="K43">
-        <v>0.19776829396609291</v>
+        <v>0.1977683253417993</v>
       </c>
       <c r="L43">
-        <v>0.2421722150478916</v>
+        <v>0.2421722594599933</v>
       </c>
       <c r="M43">
-        <v>0.24922934268282179</v>
+        <v>0.2492293590460175</v>
       </c>
       <c r="N43">
-        <v>0.25579267808371953</v>
+        <v>0.2557928764968336</v>
       </c>
       <c r="O43">
-        <v>0.23380387942614139</v>
+        <v>0.2338037009469665</v>
       </c>
       <c r="P43">
-        <v>0.2125542043203715</v>
+        <v>0.2125540202302953</v>
       </c>
       <c r="Q43">
-        <v>0.19609457945016981</v>
+        <v>0.1960947381859647</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:Q43">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>